--- a/src/iris_v2/data/equipment_data.xlsx
+++ b/src/iris_v2/data/equipment_data.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Data" sheetId="1" r:id="R6ffb08cb0ab044ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="2" r:id="R00eaacd8ba95495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="3" r:id="R08537f76d93a4144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Data" sheetId="1" r:id="R4b64c06d4dd24c01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="2" r:id="Rcab7dfc27c8d4d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="3" r:id="Rf1de16c2413443c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentDataV2" displayName="EquipmentDataV2" ref="A1:Y2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EquipmentDataV2" displayName="EquipmentDataV2" ref="A1:Y11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="25">
     <x:tableColumn id="1" name="source_id"/>
     <x:tableColumn id="2" name="substance_id"/>
@@ -438,256 +438,702 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="6"/>
-      <x:c r="B2" s="6"/>
-      <x:c r="C2"/>
-      <x:c r="D2" s="6"/>
-      <x:c r="E2"/>
-      <x:c r="F2" s="7"/>
+      <x:c r="A2" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Технологический трубопровод</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>ж.ф.</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
-      <x:c r="J2" s="7"/>
+      <x:c r="H2" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I2" s="7" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="J2" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="K2" s="7"/>
-      <x:c r="L2" s="7"/>
-      <x:c r="M2" s="7"/>
-      <x:c r="N2" s="7"/>
-      <x:c r="O2" s="7"/>
-      <x:c r="P2" s="7"/>
-      <x:c r="Q2" s="7"/>
-      <x:c r="R2" s="7"/>
-      <x:c r="S2" s="7"/>
-      <x:c r="T2" s="6"/>
-      <x:c r="U2" s="6"/>
-      <x:c r="V2" s="7"/>
-      <x:c r="W2" s="7"/>
-      <x:c r="X2" s="6"/>
-      <x:c r="Y2" s="6"/>
+      <x:c r="L2" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M2" s="7" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="N2" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O2" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P2" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q2" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R2" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S2" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T2" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U2" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V2" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W2" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X2" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y2" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="6"/>
-      <x:c r="B3" s="6"/>
-      <x:c r="D3" s="6"/>
+      <x:c r="A3" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>РВС-1000</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>ж.ф.</x:v>
+      </x:c>
       <x:c r="F3" s="7"/>
-      <x:c r="G3" s="7"/>
+      <x:c r="G3" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H3" s="7"/>
       <x:c r="I3" s="7"/>
       <x:c r="J3" s="7"/>
-      <x:c r="K3" s="7"/>
-      <x:c r="L3" s="7"/>
-      <x:c r="M3" s="7"/>
-      <x:c r="N3" s="7"/>
-      <x:c r="O3" s="7"/>
-      <x:c r="P3" s="7"/>
-      <x:c r="Q3" s="7"/>
-      <x:c r="R3" s="7"/>
-      <x:c r="S3" s="7"/>
-      <x:c r="T3" s="6"/>
-      <x:c r="U3" s="6"/>
-      <x:c r="V3" s="7"/>
-      <x:c r="W3" s="7"/>
-      <x:c r="X3" s="6"/>
-      <x:c r="Y3" s="6"/>
+      <x:c r="K3" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="L3" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M3" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q3" s="7" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R3" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S3" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T3" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U3" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V3" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W3" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X3" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y3" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="6"/>
-      <x:c r="B4" s="6"/>
-      <x:c r="D4" s="6"/>
+      <x:c r="A4" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Аппарат под давлением</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>г.ф.+ж.ф.</x:v>
+      </x:c>
       <x:c r="F4" s="7"/>
-      <x:c r="G4" s="7"/>
+      <x:c r="G4" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H4" s="7"/>
       <x:c r="I4" s="7"/>
       <x:c r="J4" s="7"/>
-      <x:c r="K4" s="7"/>
-      <x:c r="L4" s="7"/>
-      <x:c r="M4" s="7"/>
-      <x:c r="N4" s="7"/>
-      <x:c r="O4" s="7"/>
-      <x:c r="P4" s="7"/>
-      <x:c r="Q4" s="7"/>
-      <x:c r="R4" s="7"/>
-      <x:c r="S4" s="7"/>
-      <x:c r="T4" s="6"/>
-      <x:c r="U4" s="6"/>
-      <x:c r="V4" s="7"/>
-      <x:c r="W4" s="7"/>
-      <x:c r="X4" s="6"/>
-      <x:c r="Y4" s="6"/>
+      <x:c r="K4" s="7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L4" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M4" s="7" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="N4" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O4" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q4" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R4" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S4" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T4" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U4" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V4" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W4" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X4" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y4" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="6"/>
-      <x:c r="B5" s="6"/>
-      <x:c r="D5" s="6"/>
+      <x:c r="A5" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Ректификационная колонна</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>г.ф.+ж.ф.</x:v>
+      </x:c>
       <x:c r="F5" s="7"/>
-      <x:c r="G5" s="7"/>
+      <x:c r="G5" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H5" s="7"/>
       <x:c r="I5" s="7"/>
       <x:c r="J5" s="7"/>
-      <x:c r="K5" s="7"/>
-      <x:c r="L5" s="7"/>
-      <x:c r="M5" s="7"/>
-      <x:c r="N5" s="7"/>
-      <x:c r="O5" s="7"/>
-      <x:c r="P5" s="7"/>
-      <x:c r="Q5" s="7"/>
-      <x:c r="R5" s="7"/>
-      <x:c r="S5" s="7"/>
-      <x:c r="T5" s="6"/>
-      <x:c r="U5" s="6"/>
-      <x:c r="V5" s="7"/>
-      <x:c r="W5" s="7"/>
-      <x:c r="X5" s="6"/>
-      <x:c r="Y5" s="6"/>
+      <x:c r="K5" s="7" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L5" s="7" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="M5" s="7" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="N5" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O5" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="7" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q5" s="7" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R5" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S5" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T5" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U5" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V5" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W5" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X5" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y5" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="6"/>
-      <x:c r="B6" s="6"/>
-      <x:c r="D6" s="6"/>
+      <x:c r="A6" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Центробежный насос</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>ж.ф.</x:v>
+      </x:c>
       <x:c r="F6" s="7"/>
-      <x:c r="G6" s="7"/>
+      <x:c r="G6" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H6" s="7"/>
       <x:c r="I6" s="7"/>
       <x:c r="J6" s="7"/>
-      <x:c r="K6" s="7"/>
-      <x:c r="L6" s="7"/>
-      <x:c r="M6" s="7"/>
-      <x:c r="N6" s="7"/>
-      <x:c r="O6" s="7"/>
-      <x:c r="P6" s="7"/>
-      <x:c r="Q6" s="7"/>
-      <x:c r="R6" s="7"/>
-      <x:c r="S6" s="7"/>
-      <x:c r="T6" s="6"/>
-      <x:c r="U6" s="6"/>
-      <x:c r="V6" s="7"/>
-      <x:c r="W6" s="7"/>
-      <x:c r="X6" s="6"/>
-      <x:c r="Y6" s="6"/>
+      <x:c r="K6" s="7" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L6" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M6" s="7" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O6" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q6" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R6" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S6" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T6" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V6" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W6" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="6"/>
-      <x:c r="B7" s="6"/>
-      <x:c r="D7" s="6"/>
+      <x:c r="A7" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Газовый компрессор</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>г.ф.</x:v>
+      </x:c>
       <x:c r="F7" s="7"/>
-      <x:c r="G7" s="7"/>
+      <x:c r="G7" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H7" s="7"/>
       <x:c r="I7" s="7"/>
       <x:c r="J7" s="7"/>
-      <x:c r="K7" s="7"/>
-      <x:c r="L7" s="7"/>
-      <x:c r="M7" s="7"/>
-      <x:c r="N7" s="7"/>
-      <x:c r="O7" s="7"/>
-      <x:c r="P7" s="7"/>
-      <x:c r="Q7" s="7"/>
-      <x:c r="R7" s="7"/>
-      <x:c r="S7" s="7"/>
-      <x:c r="T7" s="6"/>
-      <x:c r="U7" s="6"/>
-      <x:c r="V7" s="7"/>
-      <x:c r="W7" s="7"/>
-      <x:c r="X7" s="6"/>
-      <x:c r="Y7" s="6"/>
+      <x:c r="K7" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L7" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M7" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N7" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q7" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R7" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S7" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T7" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U7" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V7" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W7" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X7" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y7" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="6"/>
-      <x:c r="B8" s="6"/>
-      <x:c r="D8" s="6"/>
+      <x:c r="A8" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Кожухотрубный теплообменник</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>г.ф.+ж.ф.</x:v>
+      </x:c>
       <x:c r="F8" s="7"/>
-      <x:c r="G8" s="7"/>
+      <x:c r="G8" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H8" s="7"/>
       <x:c r="I8" s="7"/>
       <x:c r="J8" s="7"/>
-      <x:c r="K8" s="7"/>
-      <x:c r="L8" s="7"/>
-      <x:c r="M8" s="7"/>
-      <x:c r="N8" s="7"/>
-      <x:c r="O8" s="7"/>
-      <x:c r="P8" s="7"/>
-      <x:c r="Q8" s="7"/>
-      <x:c r="R8" s="7"/>
-      <x:c r="S8" s="7"/>
-      <x:c r="T8" s="6"/>
-      <x:c r="U8" s="6"/>
-      <x:c r="V8" s="7"/>
-      <x:c r="W8" s="7"/>
-      <x:c r="X8" s="6"/>
-      <x:c r="Y8" s="6"/>
+      <x:c r="K8" s="7" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M8" s="7" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="N8" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O8" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="7" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="Q8" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R8" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T8" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U8" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V8" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X8" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y8" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="D9" s="6"/>
+      <x:c r="A9" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Железнодорожная цистерна</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>ж.ф.</x:v>
+      </x:c>
       <x:c r="F9" s="7"/>
-      <x:c r="G9" s="7"/>
+      <x:c r="G9" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H9" s="7"/>
       <x:c r="I9" s="7"/>
       <x:c r="J9" s="7"/>
-      <x:c r="K9" s="7"/>
-      <x:c r="L9" s="7"/>
-      <x:c r="M9" s="7"/>
-      <x:c r="N9" s="7"/>
-      <x:c r="O9" s="7"/>
-      <x:c r="P9" s="7"/>
-      <x:c r="Q9" s="7"/>
-      <x:c r="R9" s="7"/>
-      <x:c r="S9" s="7"/>
-      <x:c r="T9" s="6"/>
-      <x:c r="U9" s="6"/>
-      <x:c r="V9" s="7"/>
-      <x:c r="W9" s="7"/>
-      <x:c r="X9" s="6"/>
-      <x:c r="Y9" s="6"/>
+      <x:c r="K9" s="7" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L9" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M9" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O9" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q9" s="7" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R9" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S9" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T9" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U9" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V9" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W9" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X9" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y9" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="6"/>
-      <x:c r="B10" s="6"/>
-      <x:c r="D10" s="6"/>
+      <x:c r="A10" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Цистерна для СУГ</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>г.ф.+ж.ф.</x:v>
+      </x:c>
       <x:c r="F10" s="7"/>
-      <x:c r="G10" s="7"/>
+      <x:c r="G10" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H10" s="7"/>
       <x:c r="I10" s="7"/>
       <x:c r="J10" s="7"/>
-      <x:c r="K10" s="7"/>
-      <x:c r="L10" s="7"/>
-      <x:c r="M10" s="7"/>
-      <x:c r="N10" s="7"/>
-      <x:c r="O10" s="7"/>
-      <x:c r="P10" s="7"/>
-      <x:c r="Q10" s="7"/>
-      <x:c r="R10" s="7"/>
-      <x:c r="S10" s="7"/>
-      <x:c r="T10" s="6"/>
-      <x:c r="U10" s="6"/>
-      <x:c r="V10" s="7"/>
-      <x:c r="W10" s="7"/>
-      <x:c r="X10" s="6"/>
-      <x:c r="Y10" s="6"/>
+      <x:c r="K10" s="7" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="7" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M10" s="7" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="N10" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O10" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q10" s="7" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="R10" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S10" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T10" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U10" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V10" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W10" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X10" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y10" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="6"/>
-      <x:c r="B11" s="6"/>
-      <x:c r="D11" s="6"/>
-      <x:c r="F11" s="7"/>
+      <x:c r="A11" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Промысловый трубопровод</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>ж.ф.</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="G11" s="7"/>
-      <x:c r="H11" s="7"/>
-      <x:c r="I11" s="7"/>
-      <x:c r="J11" s="7"/>
+      <x:c r="H11" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="K11" s="7"/>
-      <x:c r="L11" s="7"/>
-      <x:c r="M11" s="7"/>
-      <x:c r="N11" s="7"/>
-      <x:c r="O11" s="7"/>
-      <x:c r="P11" s="7"/>
-      <x:c r="Q11" s="7"/>
-      <x:c r="R11" s="7"/>
-      <x:c r="S11" s="7"/>
-      <x:c r="T11" s="6"/>
-      <x:c r="U11" s="6"/>
-      <x:c r="V11" s="7"/>
-      <x:c r="W11" s="7"/>
-      <x:c r="X11" s="6"/>
-      <x:c r="Y11" s="6"/>
+      <x:c r="L11" s="7" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M11" s="7" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="N11" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O11" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q11" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R11" s="7" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="S11" s="7" t="str">
+        <x:v>Типовая составляющая ОПО</x:v>
+      </x:c>
+      <x:c r="T11" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U11" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V11" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W11" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X11" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y11" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6"/>
@@ -50432,7 +50878,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c63b4a4b4534a21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re709c7b57aaa4ac2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
